--- a/static/data/exports/Retro_PB_AE-BP_2024.xlsx
+++ b/static/data/exports/Retro_PB_AE-BP_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,6 +566,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
         <v>52</v>
       </c>
@@ -615,6 +618,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>52</v>
       </c>
@@ -664,6 +670,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
         <v>52</v>
       </c>
@@ -713,6 +722,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
         <v>52</v>
       </c>
@@ -762,6 +774,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>52</v>
       </c>
@@ -811,6 +826,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
         <v>52</v>
       </c>
@@ -860,6 +878,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" t="n">
         <v>52</v>
       </c>
@@ -909,6 +930,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>52</v>
       </c>
@@ -958,6 +982,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="n">
         <v>52</v>
       </c>
@@ -1007,6 +1034,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" t="n">
         <v>52</v>
       </c>
@@ -1056,6 +1086,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" t="n">
         <v>52</v>
       </c>
@@ -1105,6 +1138,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>52</v>
       </c>
@@ -1154,6 +1190,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>52</v>
       </c>
@@ -1203,6 +1242,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
         <v>52</v>
       </c>
@@ -1252,6 +1294,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>52</v>
       </c>
@@ -1301,6 +1346,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>52</v>
       </c>
@@ -1350,6 +1398,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>52</v>
       </c>
@@ -1399,6 +1450,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="n">
         <v>52</v>
       </c>
@@ -1448,6 +1502,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
       <c r="R20" t="n">
         <v>52</v>
       </c>
@@ -1497,6 +1554,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>52</v>
       </c>
@@ -1546,6 +1606,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>52</v>
       </c>
@@ -1595,6 +1658,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
       <c r="R23" t="n">
         <v>52</v>
       </c>
@@ -1644,6 +1710,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>52</v>
       </c>
@@ -1693,6 +1762,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>52</v>
       </c>
@@ -1742,6 +1814,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
       <c r="R26" t="n">
         <v>52</v>
       </c>
@@ -1791,6 +1866,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>52</v>
       </c>
@@ -1840,6 +1918,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
       <c r="R28" t="n">
         <v>52</v>
       </c>
@@ -1889,6 +1970,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
         <v>52</v>
       </c>
@@ -1938,6 +2022,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>52</v>
       </c>
@@ -1987,6 +2074,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>52</v>
       </c>
@@ -2036,6 +2126,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
       <c r="R32" t="n">
         <v>52</v>
       </c>
@@ -2085,6 +2178,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
       <c r="R33" t="n">
         <v>52</v>
       </c>
@@ -2134,6 +2230,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
       <c r="R34" t="n">
         <v>52</v>
       </c>
@@ -2183,6 +2282,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
       <c r="R35" t="n">
         <v>52</v>
       </c>
@@ -2232,6 +2334,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
       <c r="R36" t="n">
         <v>52</v>
       </c>
@@ -2281,6 +2386,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" t="n">
         <v>52</v>
       </c>
@@ -2330,6 +2438,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
       <c r="R38" t="n">
         <v>52</v>
       </c>
@@ -2379,6 +2490,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
       <c r="R39" t="n">
         <v>52</v>
       </c>
@@ -2428,6 +2542,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
       <c r="R40" t="n">
         <v>52</v>
       </c>
@@ -2477,6 +2594,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
       <c r="R41" t="n">
         <v>52</v>
       </c>
@@ -2526,6 +2646,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
       <c r="R42" t="n">
         <v>52</v>
       </c>
@@ -2575,6 +2698,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
       <c r="R43" t="n">
         <v>52</v>
       </c>
@@ -2624,6 +2750,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
       <c r="R44" t="n">
         <v>52</v>
       </c>
@@ -2673,6 +2802,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
       <c r="R45" t="n">
         <v>52</v>
       </c>
@@ -2722,6 +2854,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
       <c r="R46" t="n">
         <v>52</v>
       </c>
@@ -2771,6 +2906,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
       <c r="R47" t="n">
         <v>52</v>
       </c>
@@ -2820,6 +2958,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
       <c r="R48" t="n">
         <v>52</v>
       </c>
@@ -2869,6 +3010,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
       <c r="R49" t="n">
         <v>52</v>
       </c>
@@ -2918,6 +3062,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
       <c r="R50" t="n">
         <v>52</v>
       </c>
@@ -2967,6 +3114,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
       <c r="R51" t="n">
         <v>52</v>
       </c>
@@ -3016,6 +3166,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
       <c r="R52" t="n">
         <v>52</v>
       </c>
@@ -3065,6 +3218,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
       <c r="R53" t="n">
         <v>52</v>
       </c>
@@ -3114,6 +3270,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
       <c r="R54" t="n">
         <v>52</v>
       </c>
@@ -3163,6 +3322,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
       <c r="R55" t="n">
         <v>52</v>
       </c>
@@ -3212,6 +3374,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
       <c r="R56" t="n">
         <v>52</v>
       </c>
@@ -3261,6 +3426,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
       <c r="R57" t="n">
         <v>52</v>
       </c>
@@ -3310,6 +3478,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
       <c r="R58" t="n">
         <v>52</v>
       </c>
@@ -3359,6 +3530,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
       <c r="R59" t="n">
         <v>52</v>
       </c>
@@ -3408,6 +3582,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
       <c r="R60" t="n">
         <v>52</v>
       </c>
@@ -3457,6 +3634,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
       <c r="R61" t="n">
         <v>52</v>
       </c>
@@ -3506,6 +3686,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
       <c r="R62" t="n">
         <v>52</v>
       </c>
@@ -3555,6 +3738,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
       <c r="R63" t="n">
         <v>52</v>
       </c>
@@ -3604,6 +3790,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
       <c r="R64" t="n">
         <v>52</v>
       </c>
@@ -3653,6 +3842,9 @@
           <t>PB</t>
         </is>
       </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
       <c r="R65" t="n">
         <v>52</v>
       </c>
@@ -3701,6 +3893,9 @@
         <is>
           <t>PB</t>
         </is>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>52</v>
